--- a/education_surveys/018_training_course_interest_survey--education_surveys.xlsx
+++ b/education_surveys/018_training_course_interest_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>categories</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>categories</t>
+          <t>What category are you interested in?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>topic</t>
+          <t>topics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>topics</t>
+          <t>What topics are you interested in?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>how_often</t>
+          <t>How often would you like to attend a training course?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>preference</t>
+          <t>What is your preference for the duration of the course?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>What is your preferred email address?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Do you have any comments about the training?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>schedule</t>
+          <t>What is your schedule like?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>When would you like to start the course?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>When would you like to end the course?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>What time of day do you prefer to start the course?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>What time of day do you prefer to end the course?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>How long do you expect the course to last?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>max_participants</t>
+          <t>How many participants are you expecting in the course?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,251 +837,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Do you have any comments about the course?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,68 +896,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>categories_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'category1',_'label':_'category1'}</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'category1', 'label': 'category1'}</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>categories_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'category2',_'label':_'category2'}</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'category2', 'label': 'category2'}</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>topic_choices</t>
+          <t>topics_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'topic1',_'label':_'topic1'}</t>
+          <t>topic_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'topic1', 'label': 'topic1'}</t>
+          <t>Topic 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>topic_choices</t>
+          <t>topics_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'topic2',_'label':_'topic2'}</t>
+          <t>topic_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'topic2', 'label': 'topic2'}</t>
+          <t>Topic 2</t>
         </is>
       </c>
     </row>
@@ -1199,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'daily',_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'daily', 'label': 'daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1216,46 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'weekly',_'label':_'weekly',_'hint':_none}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'weekly', 'label': 'weekly', 'hint': None}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>comments_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'comment1',_'label':_'comment1'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'comment1', 'label': 'comment1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>comments_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'comment2',_'label':_'comment2'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'comment2', 'label': 'comment2'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
